--- a/Sheets/ops-primer-live.xlsx
+++ b/Sheets/ops-primer-live.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanDeLaCruz\Documents\Revature\excel-primer\demo\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6F0707-67DA-4E37-A55D-351D5F30A08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D531CFC-D113-4309-8A96-5454F28C35B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="12900" windowWidth="23256" windowHeight="12456" tabRatio="549" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="12900" windowWidth="23256" windowHeight="12456" tabRatio="549" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Agenda" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId13"/>
+    <pivotCache cacheId="0" r:id="rId13"/>
     <pivotCache cacheId="1" r:id="rId14"/>
   </pivotCaches>
   <extLst>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9911" uniqueCount="2364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9913" uniqueCount="2365">
   <si>
     <t>Ops Analyst Excel Primer - two days, one workbook</t>
   </si>
@@ -7176,6 +7176,9 @@
   </si>
   <si>
     <t>Total Average</t>
+  </si>
+  <si>
+    <t>ledger_date</t>
   </si>
 </sst>
 </file>
@@ -7290,7 +7293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -7338,13 +7341,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -15088,7 +15093,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59642C17-F301-463E-A3B8-03E3DB676B75}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59642C17-F301-463E-A3B8-03E3DB676B75}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -15880,7 +15885,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EC21E09-43AE-4D08-B527-2A39CDBFB3DC}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EC21E09-43AE-4D08-B527-2A39CDBFB3DC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:Q16" firstHeaderRow="1" firstDataRow="4" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -16570,7 +16575,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}" name="tblEng01" displayName="tblEng01" ref="A1:M41" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}" name="tblEng01" displayName="tblEng01" ref="A1:M41" headerRowDxfId="14">
   <autoFilter ref="A1:M41" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J41">
     <sortCondition ref="A1:A41"/>
@@ -16581,10 +16586,10 @@
     <tableColumn id="3" xr3:uid="{B8BB6B56-8344-499F-BAB4-84715457D6EF}" name="engagement_name"/>
     <tableColumn id="4" xr3:uid="{039EFC86-5137-4E51-91AE-860C7AF50C24}" name="service_line"/>
     <tableColumn id="5" xr3:uid="{6FF6A3D2-17A1-4FD9-AEAA-C1032E532018}" name="manager"/>
-    <tableColumn id="6" xr3:uid="{75A6260E-7674-4FE9-BA83-0D2F7F16F9B5}" name="start_date" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{BEA051CC-DB8F-401A-9BD4-F8DA896A9836}" name="end_date" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{A133F6EB-61F1-447E-9563-209E1FE38970}" name="budget" totalsRowFunction="sum" dataDxfId="10" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{19614B11-9DC3-43E2-AC6B-5229754C7678}" name="actual_cost" dataDxfId="9" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{75A6260E-7674-4FE9-BA83-0D2F7F16F9B5}" name="start_date" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{BEA051CC-DB8F-401A-9BD4-F8DA896A9836}" name="end_date" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{A133F6EB-61F1-447E-9563-209E1FE38970}" name="budget" totalsRowFunction="sum" dataDxfId="11" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{19614B11-9DC3-43E2-AC6B-5229754C7678}" name="actual_cost" dataDxfId="10" dataCellStyle="Comma"/>
     <tableColumn id="10" xr3:uid="{7B805801-F707-4199-B930-DC0ABE2A33AF}" name="status" totalsRowFunction="count"/>
     <tableColumn id="11" xr3:uid="{3950F076-67D4-48CF-AEED-6EB579504530}" name="variance"/>
     <tableColumn id="12" xr3:uid="{B4D02EB1-68B9-4311-8D42-EEBDC2CC34B1}" name="margin_pct"/>
@@ -16608,13 +16613,13 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="budget"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="actual_cost"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="variance" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="variance" dataDxfId="9">
       <calculatedColumnFormula>H2-I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="margin_pct" dataDxfId="7">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="margin_pct" dataDxfId="8">
       <calculatedColumnFormula>K2/H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="budget_with_uplift" dataDxfId="6">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="budget_with_uplift" dataDxfId="7">
       <calculatedColumnFormula>H2*(1+$T$2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16636,23 +16641,23 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="budget"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="actual_cost"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="variance" dataDxfId="5">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="variance" dataDxfId="6">
       <calculatedColumnFormula>IF(ISBLANK(I2), "NO COST YET", H2-I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="margin_pct" dataDxfId="4">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="margin_pct" dataDxfId="5">
       <calculatedColumnFormula>IF(ISBLANK(I2), "NO COST YET", K2/H2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="budget_with_uplift"/>
-    <tableColumn id="14" xr3:uid="{6ADA16E7-AD66-40BD-A05E-BB51EC772142}" name="client_name" dataDxfId="3">
+    <tableColumn id="14" xr3:uid="{6ADA16E7-AD66-40BD-A05E-BB51EC772142}" name="client_name" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, tblClients[client_id], tblClients[client_name], "CHECK CLIENT ID")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C3B845C8-E030-43EF-9659-5C91666A6672}" name="risk_rating" dataDxfId="2">
+    <tableColumn id="15" xr3:uid="{C3B845C8-E030-43EF-9659-5C91666A6672}" name="risk_rating" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, tblClients[client_id], tblClients[risk_rating], "No Risk Rating")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4A82E2C7-ECC2-4171-997E-328DE1C8B926}" name="id_count" dataDxfId="1">
+    <tableColumn id="16" xr3:uid="{4A82E2C7-ECC2-4171-997E-328DE1C8B926}" name="id_count" dataDxfId="2">
       <calculatedColumnFormula>COUNTIF(tblEng03[engagement_id], A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7CEF5B5F-12BC-4339-9D42-68F689835FEF}" name="id_ok" dataDxfId="0">
+    <tableColumn id="17" xr3:uid="{7CEF5B5F-12BC-4339-9D42-68F689835FEF}" name="id_ok" dataDxfId="1">
       <calculatedColumnFormula>IF(LEN(A2)=8, "OK", "CHECK LENGTH")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16704,13 +16709,19 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tblBank" displayName="tblBank" ref="A1:D121">
-  <autoFilter ref="A1:D121" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tblBank" displayName="tblBank" ref="A1:F121">
+  <autoFilter ref="A1:F121" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="bank_ref"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="post_date"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="description"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="amount"/>
+    <tableColumn id="5" xr3:uid="{ED33286F-F1AA-46F5-B515-FFC040B420F4}" name="ledger_amount" dataCellStyle="Comma">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{A9B9FD23-BE98-417A-8BA4-1F1708AF698D}" name="ledger_date" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17304,8 +17315,9 @@
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="7" width="13" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" style="22" customWidth="1"/>
+    <col min="6" max="6" width="13" style="21" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="2" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
@@ -17315,7 +17327,7 @@
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
     <col min="17" max="17" width="2" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" customWidth="1"/>
     <col min="19" max="19" width="17" customWidth="1"/>
     <col min="20" max="20" width="13" customWidth="1"/>
     <col min="21" max="21" width="26" customWidth="1"/>
@@ -17338,6 +17350,12 @@
       <c r="D1" t="s">
         <v>233</v>
       </c>
+      <c r="E1" s="22" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>2364</v>
+      </c>
       <c r="J1" t="s">
         <v>1372</v>
       </c>
@@ -17393,6 +17411,14 @@
       </c>
       <c r="D2" s="18">
         <v>11671.47</v>
+      </c>
+      <c r="E2" s="22">
+        <f>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>11671.47</v>
+      </c>
+      <c r="F2" s="21">
+        <f>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
       </c>
       <c r="J2" t="s">
         <v>1386</v>
@@ -17434,6 +17460,14 @@
       <c r="D3" s="18">
         <v>831.04</v>
       </c>
+      <c r="E3" s="22">
+        <f>_xlfn.XLOOKUP(A3, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>831.04</v>
+      </c>
+      <c r="F3" s="21">
+        <f>_xlfn.XLOOKUP(A3, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J3" t="s">
         <v>1391</v>
       </c>
@@ -17474,6 +17508,14 @@
       <c r="D4" s="18">
         <v>45863.57</v>
       </c>
+      <c r="E4" s="22">
+        <f>_xlfn.XLOOKUP(A4, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>45863.57</v>
+      </c>
+      <c r="F4" s="21">
+        <f>_xlfn.XLOOKUP(A4, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J4" t="s">
         <v>1397</v>
       </c>
@@ -17514,6 +17556,14 @@
       <c r="D5" s="18">
         <v>15148.37</v>
       </c>
+      <c r="E5" s="22">
+        <f>_xlfn.XLOOKUP(A5, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>15148.37</v>
+      </c>
+      <c r="F5" s="21">
+        <f>_xlfn.XLOOKUP(A5, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J5" t="s">
         <v>1403</v>
       </c>
@@ -17554,6 +17604,14 @@
       <c r="D6" s="18">
         <v>13527.97</v>
       </c>
+      <c r="E6" s="22">
+        <f>_xlfn.XLOOKUP(A6, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>13527.97</v>
+      </c>
+      <c r="F6" s="21">
+        <f>_xlfn.XLOOKUP(A6, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J6" t="s">
         <v>1408</v>
       </c>
@@ -17591,6 +17649,14 @@
       </c>
       <c r="D7" s="18">
         <v>20092.939999999999</v>
+      </c>
+      <c r="E7" s="22">
+        <f>_xlfn.XLOOKUP(A7, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>20092.939999999999</v>
+      </c>
+      <c r="F7" s="21">
+        <f>_xlfn.XLOOKUP(A7, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
       </c>
       <c r="J7" t="s">
         <v>1412</v>
@@ -17632,6 +17698,14 @@
       <c r="D8" s="18">
         <v>28659.66</v>
       </c>
+      <c r="E8" s="22">
+        <f>_xlfn.XLOOKUP(A8, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>28659.66</v>
+      </c>
+      <c r="F8" s="21">
+        <f>_xlfn.XLOOKUP(A8, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J8" t="s">
         <v>1417</v>
       </c>
@@ -17672,6 +17746,14 @@
       <c r="D9" s="18">
         <v>47336.97</v>
       </c>
+      <c r="E9" s="22">
+        <f>_xlfn.XLOOKUP(A9, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>47336.97</v>
+      </c>
+      <c r="F9" s="21">
+        <f>_xlfn.XLOOKUP(A9, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J9" t="s">
         <v>1422</v>
       </c>
@@ -17712,6 +17794,14 @@
       <c r="D10" s="18">
         <v>34034.300000000003</v>
       </c>
+      <c r="E10" s="22">
+        <f>_xlfn.XLOOKUP(A10, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>34034.300000000003</v>
+      </c>
+      <c r="F10" s="21">
+        <f>_xlfn.XLOOKUP(A10, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J10" t="s">
         <v>1427</v>
       </c>
@@ -17752,6 +17842,14 @@
       <c r="D11" s="18">
         <v>15449.79</v>
       </c>
+      <c r="E11" s="22">
+        <f>_xlfn.XLOOKUP(A11, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>15449.79</v>
+      </c>
+      <c r="F11" s="21">
+        <f>_xlfn.XLOOKUP(A11, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J11" t="s">
         <v>1432</v>
       </c>
@@ -17792,6 +17890,14 @@
       <c r="D12" s="18">
         <v>25781.37</v>
       </c>
+      <c r="E12" s="22">
+        <f>_xlfn.XLOOKUP(A12, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>25781.37</v>
+      </c>
+      <c r="F12" s="21">
+        <f>_xlfn.XLOOKUP(A12, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J12" t="s">
         <v>1437</v>
       </c>
@@ -17829,6 +17935,14 @@
       </c>
       <c r="D13" s="18">
         <v>21674.73</v>
+      </c>
+      <c r="E13" s="22">
+        <f>_xlfn.XLOOKUP(A13, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>21674.73</v>
+      </c>
+      <c r="F13" s="21">
+        <f>_xlfn.XLOOKUP(A13, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
       </c>
       <c r="J13" t="s">
         <v>1442</v>
@@ -17870,6 +17984,14 @@
       <c r="D14" s="18">
         <v>24200.78</v>
       </c>
+      <c r="E14" s="22">
+        <f>_xlfn.XLOOKUP(A14, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>24200.78</v>
+      </c>
+      <c r="F14" s="21">
+        <f>_xlfn.XLOOKUP(A14, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J14" t="s">
         <v>1448</v>
       </c>
@@ -17910,6 +18032,14 @@
       <c r="D15" s="18">
         <v>20190.79</v>
       </c>
+      <c r="E15" s="22">
+        <f>_xlfn.XLOOKUP(A15, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>20190.79</v>
+      </c>
+      <c r="F15" s="21">
+        <f>_xlfn.XLOOKUP(A15, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J15" t="s">
         <v>1453</v>
       </c>
@@ -17950,6 +18080,14 @@
       <c r="D16" s="18">
         <v>8253.75</v>
       </c>
+      <c r="E16" s="22">
+        <f>_xlfn.XLOOKUP(A16, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>8253.75</v>
+      </c>
+      <c r="F16" s="21">
+        <f>_xlfn.XLOOKUP(A16, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J16" t="s">
         <v>1457</v>
       </c>
@@ -17988,6 +18126,14 @@
       <c r="D17" s="18">
         <v>19134.36</v>
       </c>
+      <c r="E17" s="22">
+        <f>_xlfn.XLOOKUP(A17, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>19134.36</v>
+      </c>
+      <c r="F17" s="21">
+        <f>_xlfn.XLOOKUP(A17, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J17" t="s">
         <v>1460</v>
       </c>
@@ -18020,6 +18166,14 @@
       <c r="D18" s="18">
         <v>18829</v>
       </c>
+      <c r="E18" s="22" t="str">
+        <f>_xlfn.XLOOKUP(A18, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>NOT IN LEDGER</v>
+      </c>
+      <c r="F18" s="21" t="str">
+        <f>_xlfn.XLOOKUP(A18, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>DATE NOT FOUND</v>
+      </c>
       <c r="J18" t="s">
         <v>1465</v>
       </c>
@@ -18052,6 +18206,14 @@
       <c r="D19" s="18">
         <v>9834.35</v>
       </c>
+      <c r="E19" s="22">
+        <f>_xlfn.XLOOKUP(A19, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>9834.35</v>
+      </c>
+      <c r="F19" s="21">
+        <f>_xlfn.XLOOKUP(A19, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J19" t="s">
         <v>1470</v>
       </c>
@@ -18084,6 +18246,14 @@
       <c r="D20" s="18">
         <v>39257.870000000003</v>
       </c>
+      <c r="E20" s="22">
+        <f>_xlfn.XLOOKUP(A20, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>39257.870000000003</v>
+      </c>
+      <c r="F20" s="21">
+        <f>_xlfn.XLOOKUP(A20, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J20" t="s">
         <v>1474</v>
       </c>
@@ -18098,6 +18268,18 @@
       </c>
       <c r="N20" s="18">
         <v>13578.64</v>
+      </c>
+      <c r="R20" s="18">
+        <f>SUM(tblBank[amount])</f>
+        <v>2755208.6699999995</v>
+      </c>
+      <c r="S20" s="18">
+        <f>SUM(tblLedger[amount])</f>
+        <v>2720606.96</v>
+      </c>
+      <c r="T20" s="18">
+        <f>R20-S20</f>
+        <v>34601.709999999497</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
@@ -18113,6 +18295,14 @@
       <c r="D21" s="18">
         <v>17439.57</v>
       </c>
+      <c r="E21" s="22">
+        <f>_xlfn.XLOOKUP(A21, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>17439.57</v>
+      </c>
+      <c r="F21" s="21">
+        <f>_xlfn.XLOOKUP(A21, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J21" t="s">
         <v>1478</v>
       </c>
@@ -18142,6 +18332,14 @@
       <c r="D22" s="18">
         <v>7483.48</v>
       </c>
+      <c r="E22" s="22">
+        <f>_xlfn.XLOOKUP(A22, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>7483.48</v>
+      </c>
+      <c r="F22" s="21">
+        <f>_xlfn.XLOOKUP(A22, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J22" t="s">
         <v>1482</v>
       </c>
@@ -18171,6 +18369,14 @@
       <c r="D23" s="18">
         <v>27318.25</v>
       </c>
+      <c r="E23" s="22">
+        <f>_xlfn.XLOOKUP(A23, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>27318.25</v>
+      </c>
+      <c r="F23" s="21">
+        <f>_xlfn.XLOOKUP(A23, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J23" t="s">
         <v>1486</v>
       </c>
@@ -18200,6 +18406,14 @@
       <c r="D24" s="18">
         <v>40591.269999999997</v>
       </c>
+      <c r="E24" s="22">
+        <f>_xlfn.XLOOKUP(A24, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>40591.269999999997</v>
+      </c>
+      <c r="F24" s="21">
+        <f>_xlfn.XLOOKUP(A24, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J24" t="s">
         <v>1490</v>
       </c>
@@ -18229,6 +18443,14 @@
       <c r="D25" s="18">
         <v>37521.79</v>
       </c>
+      <c r="E25" s="22">
+        <f>_xlfn.XLOOKUP(A25, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>37521.79</v>
+      </c>
+      <c r="F25" s="21">
+        <f>_xlfn.XLOOKUP(A25, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J25" t="s">
         <v>1494</v>
       </c>
@@ -18258,6 +18480,14 @@
       <c r="D26" s="18">
         <v>29952.42</v>
       </c>
+      <c r="E26" s="22">
+        <f>_xlfn.XLOOKUP(A26, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>29952.42</v>
+      </c>
+      <c r="F26" s="21">
+        <f>_xlfn.XLOOKUP(A26, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J26" t="s">
         <v>1498</v>
       </c>
@@ -18287,6 +18517,14 @@
       <c r="D27" s="18">
         <v>35157.06</v>
       </c>
+      <c r="E27" s="22">
+        <f>_xlfn.XLOOKUP(A27, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>35157.06</v>
+      </c>
+      <c r="F27" s="21">
+        <f>_xlfn.XLOOKUP(A27, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J27" t="s">
         <v>1502</v>
       </c>
@@ -18316,6 +18554,14 @@
       <c r="D28" s="18">
         <v>16299.47</v>
       </c>
+      <c r="E28" s="22">
+        <f>_xlfn.XLOOKUP(A28, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>16299.47</v>
+      </c>
+      <c r="F28" s="21">
+        <f>_xlfn.XLOOKUP(A28, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J28" t="s">
         <v>1505</v>
       </c>
@@ -18345,6 +18591,14 @@
       <c r="D29" s="18">
         <v>7064.47</v>
       </c>
+      <c r="E29" s="22">
+        <f>_xlfn.XLOOKUP(A29, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>7064.47</v>
+      </c>
+      <c r="F29" s="21">
+        <f>_xlfn.XLOOKUP(A29, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J29" t="s">
         <v>1508</v>
       </c>
@@ -18374,6 +18628,14 @@
       <c r="D30" s="18">
         <v>12426.71</v>
       </c>
+      <c r="E30" s="22">
+        <f>_xlfn.XLOOKUP(A30, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>12426.71</v>
+      </c>
+      <c r="F30" s="21">
+        <f>_xlfn.XLOOKUP(A30, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J30" t="s">
         <v>1511</v>
       </c>
@@ -18403,6 +18665,14 @@
       <c r="D31" s="18">
         <v>16931.64</v>
       </c>
+      <c r="E31" s="22">
+        <f>_xlfn.XLOOKUP(A31, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>16931.64</v>
+      </c>
+      <c r="F31" s="21">
+        <f>_xlfn.XLOOKUP(A31, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J31" t="s">
         <v>1514</v>
       </c>
@@ -18432,6 +18702,14 @@
       <c r="D32" s="18">
         <v>13578.64</v>
       </c>
+      <c r="E32" s="22">
+        <f>_xlfn.XLOOKUP(A32, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>13578.64</v>
+      </c>
+      <c r="F32" s="21">
+        <f>_xlfn.XLOOKUP(A32, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J32" t="s">
         <v>1517</v>
       </c>
@@ -18461,6 +18739,14 @@
       <c r="D33" s="18">
         <v>22585.61</v>
       </c>
+      <c r="E33" s="22">
+        <f>_xlfn.XLOOKUP(A33, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>22585.61</v>
+      </c>
+      <c r="F33" s="21">
+        <f>_xlfn.XLOOKUP(A33, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J33" t="s">
         <v>1520</v>
       </c>
@@ -18490,6 +18776,14 @@
       <c r="D34" s="18">
         <v>7366.29</v>
       </c>
+      <c r="E34" s="22">
+        <f>_xlfn.XLOOKUP(A34, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>7816.29</v>
+      </c>
+      <c r="F34" s="21">
+        <f>_xlfn.XLOOKUP(A34, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J34" t="s">
         <v>1524</v>
       </c>
@@ -18519,6 +18813,14 @@
       <c r="D35" s="18">
         <v>6470</v>
       </c>
+      <c r="E35" s="22">
+        <f>_xlfn.XLOOKUP(A35, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>6470</v>
+      </c>
+      <c r="F35" s="21">
+        <f>_xlfn.XLOOKUP(A35, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J35" t="s">
         <v>1528</v>
       </c>
@@ -18548,6 +18850,14 @@
       <c r="D36" s="18">
         <v>12317.56</v>
       </c>
+      <c r="E36" s="22">
+        <f>_xlfn.XLOOKUP(A36, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>12317.56</v>
+      </c>
+      <c r="F36" s="21">
+        <f>_xlfn.XLOOKUP(A36, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J36" t="s">
         <v>1532</v>
       </c>
@@ -18577,6 +18887,14 @@
       <c r="D37" s="18">
         <v>9633.0499999999993</v>
       </c>
+      <c r="E37" s="22">
+        <f>_xlfn.XLOOKUP(A37, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>9633.0499999999993</v>
+      </c>
+      <c r="F37" s="21">
+        <f>_xlfn.XLOOKUP(A37, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J37" t="s">
         <v>1536</v>
       </c>
@@ -18606,6 +18924,14 @@
       <c r="D38" s="18">
         <v>38531.199999999997</v>
       </c>
+      <c r="E38" s="22">
+        <f>_xlfn.XLOOKUP(A38, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>38531.199999999997</v>
+      </c>
+      <c r="F38" s="21">
+        <f>_xlfn.XLOOKUP(A38, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J38" t="s">
         <v>1539</v>
       </c>
@@ -18635,6 +18961,14 @@
       <c r="D39" s="18">
         <v>25918.34</v>
       </c>
+      <c r="E39" s="22">
+        <f>_xlfn.XLOOKUP(A39, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>25918.34</v>
+      </c>
+      <c r="F39" s="21">
+        <f>_xlfn.XLOOKUP(A39, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J39" t="s">
         <v>1542</v>
       </c>
@@ -18664,6 +18998,14 @@
       <c r="D40" s="18">
         <v>9724.14</v>
       </c>
+      <c r="E40" s="22">
+        <f>_xlfn.XLOOKUP(A40, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>9724.14</v>
+      </c>
+      <c r="F40" s="21">
+        <f>_xlfn.XLOOKUP(A40, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J40" t="s">
         <v>1545</v>
       </c>
@@ -18693,6 +19035,14 @@
       <c r="D41" s="18">
         <v>20745.12</v>
       </c>
+      <c r="E41" s="22">
+        <f>_xlfn.XLOOKUP(A41, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>20745.12</v>
+      </c>
+      <c r="F41" s="21">
+        <f>_xlfn.XLOOKUP(A41, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J41" t="s">
         <v>1549</v>
       </c>
@@ -18722,6 +19072,14 @@
       <c r="D42" s="18">
         <v>41883.97</v>
       </c>
+      <c r="E42" s="22">
+        <f>_xlfn.XLOOKUP(A42, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>41883.97</v>
+      </c>
+      <c r="F42" s="21">
+        <f>_xlfn.XLOOKUP(A42, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J42" t="s">
         <v>1553</v>
       </c>
@@ -18751,6 +19109,14 @@
       <c r="D43" s="18">
         <v>27830.98</v>
       </c>
+      <c r="E43" s="22">
+        <f>_xlfn.XLOOKUP(A43, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>27830.98</v>
+      </c>
+      <c r="F43" s="21">
+        <f>_xlfn.XLOOKUP(A43, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J43" t="s">
         <v>1557</v>
       </c>
@@ -18780,6 +19146,14 @@
       <c r="D44" s="18">
         <v>26699.41</v>
       </c>
+      <c r="E44" s="22">
+        <f>_xlfn.XLOOKUP(A44, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>26699.41</v>
+      </c>
+      <c r="F44" s="21">
+        <f>_xlfn.XLOOKUP(A44, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J44" t="s">
         <v>1560</v>
       </c>
@@ -18809,6 +19183,14 @@
       <c r="D45" s="18">
         <v>18935.439999999999</v>
       </c>
+      <c r="E45" s="22">
+        <f>_xlfn.XLOOKUP(A45, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>18935.439999999999</v>
+      </c>
+      <c r="F45" s="21">
+        <f>_xlfn.XLOOKUP(A45, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J45" t="s">
         <v>1563</v>
       </c>
@@ -18838,6 +19220,14 @@
       <c r="D46" s="18">
         <v>9601.24</v>
       </c>
+      <c r="E46" s="22">
+        <f>_xlfn.XLOOKUP(A46, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>9601.24</v>
+      </c>
+      <c r="F46" s="21">
+        <f>_xlfn.XLOOKUP(A46, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J46" t="s">
         <v>1566</v>
       </c>
@@ -18867,6 +19257,14 @@
       <c r="D47" s="18">
         <v>30113.09</v>
       </c>
+      <c r="E47" s="22">
+        <f>_xlfn.XLOOKUP(A47, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>30113.09</v>
+      </c>
+      <c r="F47" s="21">
+        <f>_xlfn.XLOOKUP(A47, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J47" t="s">
         <v>1568</v>
       </c>
@@ -18896,6 +19294,14 @@
       <c r="D48" s="18">
         <v>3933.88</v>
       </c>
+      <c r="E48" s="22">
+        <f>_xlfn.XLOOKUP(A48, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>3933.88</v>
+      </c>
+      <c r="F48" s="21">
+        <f>_xlfn.XLOOKUP(A48, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J48" t="s">
         <v>1570</v>
       </c>
@@ -18925,6 +19331,14 @@
       <c r="D49" s="18">
         <v>37790.57</v>
       </c>
+      <c r="E49" s="22">
+        <f>_xlfn.XLOOKUP(A49, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>37790.57</v>
+      </c>
+      <c r="F49" s="21">
+        <f>_xlfn.XLOOKUP(A49, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J49" t="s">
         <v>1573</v>
       </c>
@@ -18954,6 +19368,14 @@
       <c r="D50" s="18">
         <v>2996.81</v>
       </c>
+      <c r="E50" s="22">
+        <f>_xlfn.XLOOKUP(A50, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>2996.81</v>
+      </c>
+      <c r="F50" s="21">
+        <f>_xlfn.XLOOKUP(A50, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J50" t="s">
         <v>1576</v>
       </c>
@@ -18983,6 +19405,14 @@
       <c r="D51" s="18">
         <v>35888.080000000002</v>
       </c>
+      <c r="E51" s="22">
+        <f>_xlfn.XLOOKUP(A51, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>35888.080000000002</v>
+      </c>
+      <c r="F51" s="21">
+        <f>_xlfn.XLOOKUP(A51, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J51" t="s">
         <v>1580</v>
       </c>
@@ -19012,6 +19442,14 @@
       <c r="D52" s="18">
         <v>18520.54</v>
       </c>
+      <c r="E52" s="22">
+        <f>_xlfn.XLOOKUP(A52, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>18520.54</v>
+      </c>
+      <c r="F52" s="21">
+        <f>_xlfn.XLOOKUP(A52, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J52" t="s">
         <v>1584</v>
       </c>
@@ -19041,6 +19479,14 @@
       <c r="D53" s="18">
         <v>32835.15</v>
       </c>
+      <c r="E53" s="22">
+        <f>_xlfn.XLOOKUP(A53, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>32835.15</v>
+      </c>
+      <c r="F53" s="21">
+        <f>_xlfn.XLOOKUP(A53, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J53" t="s">
         <v>1588</v>
       </c>
@@ -19070,6 +19516,14 @@
       <c r="D54" s="18">
         <v>28470.51</v>
       </c>
+      <c r="E54" s="22">
+        <f>_xlfn.XLOOKUP(A54, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>28470.51</v>
+      </c>
+      <c r="F54" s="21">
+        <f>_xlfn.XLOOKUP(A54, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J54" t="s">
         <v>1592</v>
       </c>
@@ -19099,6 +19553,14 @@
       <c r="D55" s="18">
         <v>6418.14</v>
       </c>
+      <c r="E55" s="22">
+        <f>_xlfn.XLOOKUP(A55, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>6418.14</v>
+      </c>
+      <c r="F55" s="21">
+        <f>_xlfn.XLOOKUP(A55, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J55" t="s">
         <v>1596</v>
       </c>
@@ -19128,6 +19590,14 @@
       <c r="D56" s="18">
         <v>25963.48</v>
       </c>
+      <c r="E56" s="22">
+        <f>_xlfn.XLOOKUP(A56, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>25963.48</v>
+      </c>
+      <c r="F56" s="21">
+        <f>_xlfn.XLOOKUP(A56, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J56" t="s">
         <v>1600</v>
       </c>
@@ -19157,6 +19627,14 @@
       <c r="D57" s="18">
         <v>3791.5</v>
       </c>
+      <c r="E57" s="22">
+        <f>_xlfn.XLOOKUP(A57, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>3791.5</v>
+      </c>
+      <c r="F57" s="21">
+        <f>_xlfn.XLOOKUP(A57, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J57" t="s">
         <v>1603</v>
       </c>
@@ -19186,6 +19664,14 @@
       <c r="D58" s="18">
         <v>11768.17</v>
       </c>
+      <c r="E58" s="22">
+        <f>_xlfn.XLOOKUP(A58, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>11768.17</v>
+      </c>
+      <c r="F58" s="21">
+        <f>_xlfn.XLOOKUP(A58, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J58" t="s">
         <v>1605</v>
       </c>
@@ -19215,6 +19701,14 @@
       <c r="D59" s="18">
         <v>18474.689999999999</v>
       </c>
+      <c r="E59" s="22" t="str">
+        <f>_xlfn.XLOOKUP(A59, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>NOT IN LEDGER</v>
+      </c>
+      <c r="F59" s="21" t="str">
+        <f>_xlfn.XLOOKUP(A59, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>DATE NOT FOUND</v>
+      </c>
       <c r="J59" t="s">
         <v>1608</v>
       </c>
@@ -19244,6 +19738,14 @@
       <c r="D60" s="18">
         <v>13890.8</v>
       </c>
+      <c r="E60" s="22">
+        <f>_xlfn.XLOOKUP(A60, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>13890.8</v>
+      </c>
+      <c r="F60" s="21">
+        <f>_xlfn.XLOOKUP(A60, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J60" t="s">
         <v>1610</v>
       </c>
@@ -19273,6 +19775,14 @@
       <c r="D61" s="18">
         <v>31849.01</v>
       </c>
+      <c r="E61" s="22">
+        <f>_xlfn.XLOOKUP(A61, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>31849.01</v>
+      </c>
+      <c r="F61" s="21">
+        <f>_xlfn.XLOOKUP(A61, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J61" t="s">
         <v>1613</v>
       </c>
@@ -19302,6 +19812,14 @@
       <c r="D62" s="18">
         <v>47371.360000000001</v>
       </c>
+      <c r="E62" s="22">
+        <f>_xlfn.XLOOKUP(A62, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>47371.360000000001</v>
+      </c>
+      <c r="F62" s="21">
+        <f>_xlfn.XLOOKUP(A62, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J62" t="s">
         <v>1616</v>
       </c>
@@ -19331,6 +19849,14 @@
       <c r="D63" s="18">
         <v>17290.14</v>
       </c>
+      <c r="E63" s="22">
+        <f>_xlfn.XLOOKUP(A63, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>17290.14</v>
+      </c>
+      <c r="F63" s="21">
+        <f>_xlfn.XLOOKUP(A63, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J63" t="s">
         <v>1619</v>
       </c>
@@ -19360,6 +19886,14 @@
       <c r="D64" s="18">
         <v>40293.01</v>
       </c>
+      <c r="E64" s="22">
+        <f>_xlfn.XLOOKUP(A64, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>40293.01</v>
+      </c>
+      <c r="F64" s="21">
+        <f>_xlfn.XLOOKUP(A64, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J64" t="s">
         <v>1622</v>
       </c>
@@ -19389,6 +19923,14 @@
       <c r="D65" s="18">
         <v>10998.49</v>
       </c>
+      <c r="E65" s="22">
+        <f>_xlfn.XLOOKUP(A65, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>10998.49</v>
+      </c>
+      <c r="F65" s="21">
+        <f>_xlfn.XLOOKUP(A65, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J65" t="s">
         <v>1626</v>
       </c>
@@ -19418,6 +19960,14 @@
       <c r="D66" s="18">
         <v>34120.550000000003</v>
       </c>
+      <c r="E66" s="22">
+        <f>_xlfn.XLOOKUP(A66, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>34120.550000000003</v>
+      </c>
+      <c r="F66" s="21">
+        <f>_xlfn.XLOOKUP(A66, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J66" t="s">
         <v>1629</v>
       </c>
@@ -19447,6 +19997,14 @@
       <c r="D67" s="18">
         <v>16853.650000000001</v>
       </c>
+      <c r="E67" s="22">
+        <f>_xlfn.XLOOKUP(A67, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>16853.650000000001</v>
+      </c>
+      <c r="F67" s="21">
+        <f>_xlfn.XLOOKUP(A67, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J67" t="s">
         <v>1632</v>
       </c>
@@ -19476,6 +20034,14 @@
       <c r="D68" s="18">
         <v>25813.599999999999</v>
       </c>
+      <c r="E68" s="22">
+        <f>_xlfn.XLOOKUP(A68, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>25813.599999999999</v>
+      </c>
+      <c r="F68" s="21">
+        <f>_xlfn.XLOOKUP(A68, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J68" t="s">
         <v>1635</v>
       </c>
@@ -19505,6 +20071,14 @@
       <c r="D69" s="18">
         <v>4479.8599999999997</v>
       </c>
+      <c r="E69" s="22">
+        <f>_xlfn.XLOOKUP(A69, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>4479.8599999999997</v>
+      </c>
+      <c r="F69" s="21">
+        <f>_xlfn.XLOOKUP(A69, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J69" t="s">
         <v>1638</v>
       </c>
@@ -19534,6 +20108,14 @@
       <c r="D70" s="18">
         <v>39756.120000000003</v>
       </c>
+      <c r="E70" s="22">
+        <f>_xlfn.XLOOKUP(A70, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>39756.120000000003</v>
+      </c>
+      <c r="F70" s="21">
+        <f>_xlfn.XLOOKUP(A70, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J70" t="s">
         <v>1641</v>
       </c>
@@ -19563,6 +20145,14 @@
       <c r="D71" s="18">
         <v>10221.879999999999</v>
       </c>
+      <c r="E71" s="22">
+        <f>_xlfn.XLOOKUP(A71, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>10221.879999999999</v>
+      </c>
+      <c r="F71" s="21">
+        <f>_xlfn.XLOOKUP(A71, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J71" t="s">
         <v>1645</v>
       </c>
@@ -19592,6 +20182,14 @@
       <c r="D72" s="18">
         <v>22379.87</v>
       </c>
+      <c r="E72" s="22">
+        <f>_xlfn.XLOOKUP(A72, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>21129.87</v>
+      </c>
+      <c r="F72" s="21">
+        <f>_xlfn.XLOOKUP(A72, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J72" t="s">
         <v>1648</v>
       </c>
@@ -19621,6 +20219,14 @@
       <c r="D73" s="18">
         <v>14111.62</v>
       </c>
+      <c r="E73" s="22">
+        <f>_xlfn.XLOOKUP(A73, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>14111.62</v>
+      </c>
+      <c r="F73" s="21">
+        <f>_xlfn.XLOOKUP(A73, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J73" t="s">
         <v>1651</v>
       </c>
@@ -19650,6 +20256,14 @@
       <c r="D74" s="18">
         <v>38937.19</v>
       </c>
+      <c r="E74" s="22">
+        <f>_xlfn.XLOOKUP(A74, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>38937.19</v>
+      </c>
+      <c r="F74" s="21">
+        <f>_xlfn.XLOOKUP(A74, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J74" t="s">
         <v>1654</v>
       </c>
@@ -19679,6 +20293,14 @@
       <c r="D75" s="18">
         <v>28546.400000000001</v>
       </c>
+      <c r="E75" s="22">
+        <f>_xlfn.XLOOKUP(A75, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>28546.400000000001</v>
+      </c>
+      <c r="F75" s="21">
+        <f>_xlfn.XLOOKUP(A75, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J75" t="s">
         <v>1656</v>
       </c>
@@ -19708,6 +20330,14 @@
       <c r="D76" s="18">
         <v>29625.08</v>
       </c>
+      <c r="E76" s="22">
+        <f>_xlfn.XLOOKUP(A76, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>29625.08</v>
+      </c>
+      <c r="F76" s="21">
+        <f>_xlfn.XLOOKUP(A76, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J76" t="s">
         <v>1658</v>
       </c>
@@ -19737,6 +20367,14 @@
       <c r="D77" s="18">
         <v>36289.24</v>
       </c>
+      <c r="E77" s="22">
+        <f>_xlfn.XLOOKUP(A77, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>36289.24</v>
+      </c>
+      <c r="F77" s="21">
+        <f>_xlfn.XLOOKUP(A77, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J77" t="s">
         <v>1660</v>
       </c>
@@ -19766,6 +20404,14 @@
       <c r="D78" s="18">
         <v>12421.31</v>
       </c>
+      <c r="E78" s="22">
+        <f>_xlfn.XLOOKUP(A78, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>12421.31</v>
+      </c>
+      <c r="F78" s="21">
+        <f>_xlfn.XLOOKUP(A78, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J78" t="s">
         <v>1662</v>
       </c>
@@ -19795,6 +20441,14 @@
       <c r="D79" s="18">
         <v>3031.35</v>
       </c>
+      <c r="E79" s="22">
+        <f>_xlfn.XLOOKUP(A79, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>3031.35</v>
+      </c>
+      <c r="F79" s="21">
+        <f>_xlfn.XLOOKUP(A79, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J79" t="s">
         <v>1664</v>
       </c>
@@ -19824,6 +20478,14 @@
       <c r="D80" s="18">
         <v>39813.519999999997</v>
       </c>
+      <c r="E80" s="22">
+        <f>_xlfn.XLOOKUP(A80, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>39813.519999999997</v>
+      </c>
+      <c r="F80" s="21">
+        <f>_xlfn.XLOOKUP(A80, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J80" t="s">
         <v>1667</v>
       </c>
@@ -19853,6 +20515,14 @@
       <c r="D81" s="18">
         <v>15320.15</v>
       </c>
+      <c r="E81" s="22">
+        <f>_xlfn.XLOOKUP(A81, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>15320.15</v>
+      </c>
+      <c r="F81" s="21">
+        <f>_xlfn.XLOOKUP(A81, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J81" t="s">
         <v>1671</v>
       </c>
@@ -19882,6 +20552,14 @@
       <c r="D82" s="18">
         <v>39035.949999999997</v>
       </c>
+      <c r="E82" s="22">
+        <f>_xlfn.XLOOKUP(A82, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>39035.949999999997</v>
+      </c>
+      <c r="F82" s="21">
+        <f>_xlfn.XLOOKUP(A82, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J82" t="s">
         <v>1675</v>
       </c>
@@ -19911,6 +20589,14 @@
       <c r="D83" s="18">
         <v>45929.53</v>
       </c>
+      <c r="E83" s="22">
+        <f>_xlfn.XLOOKUP(A83, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>45929.53</v>
+      </c>
+      <c r="F83" s="21">
+        <f>_xlfn.XLOOKUP(A83, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J83" t="s">
         <v>1679</v>
       </c>
@@ -19940,6 +20626,14 @@
       <c r="D84" s="18">
         <v>30293.88</v>
       </c>
+      <c r="E84" s="22">
+        <f>_xlfn.XLOOKUP(A84, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>30293.88</v>
+      </c>
+      <c r="F84" s="21">
+        <f>_xlfn.XLOOKUP(A84, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J84" t="s">
         <v>1682</v>
       </c>
@@ -19969,6 +20663,14 @@
       <c r="D85" s="18">
         <v>5182.1899999999996</v>
       </c>
+      <c r="E85" s="22">
+        <f>_xlfn.XLOOKUP(A85, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>5182.1899999999996</v>
+      </c>
+      <c r="F85" s="21">
+        <f>_xlfn.XLOOKUP(A85, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J85" t="s">
         <v>1685</v>
       </c>
@@ -19998,6 +20700,14 @@
       <c r="D86" s="18">
         <v>41027.89</v>
       </c>
+      <c r="E86" s="22">
+        <f>_xlfn.XLOOKUP(A86, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>41027.89</v>
+      </c>
+      <c r="F86" s="21">
+        <f>_xlfn.XLOOKUP(A86, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J86" t="s">
         <v>1687</v>
       </c>
@@ -20027,6 +20737,14 @@
       <c r="D87" s="18">
         <v>30496.19</v>
       </c>
+      <c r="E87" s="22">
+        <f>_xlfn.XLOOKUP(A87, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>30496.19</v>
+      </c>
+      <c r="F87" s="21">
+        <f>_xlfn.XLOOKUP(A87, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J87" t="s">
         <v>1689</v>
       </c>
@@ -20056,6 +20774,14 @@
       <c r="D88" s="18">
         <v>11991.69</v>
       </c>
+      <c r="E88" s="22">
+        <f>_xlfn.XLOOKUP(A88, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>11991.69</v>
+      </c>
+      <c r="F88" s="21">
+        <f>_xlfn.XLOOKUP(A88, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J88" t="s">
         <v>1691</v>
       </c>
@@ -20085,6 +20811,14 @@
       <c r="D89" s="18">
         <v>10175.89</v>
       </c>
+      <c r="E89" s="22">
+        <f>_xlfn.XLOOKUP(A89, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>10175.89</v>
+      </c>
+      <c r="F89" s="21">
+        <f>_xlfn.XLOOKUP(A89, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J89" t="s">
         <v>1693</v>
       </c>
@@ -20114,6 +20848,14 @@
       <c r="D90" s="18">
         <v>24493.69</v>
       </c>
+      <c r="E90" s="22">
+        <f>_xlfn.XLOOKUP(A90, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>24493.69</v>
+      </c>
+      <c r="F90" s="21">
+        <f>_xlfn.XLOOKUP(A90, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J90" t="s">
         <v>1696</v>
       </c>
@@ -20143,6 +20885,14 @@
       <c r="D91" s="18">
         <v>6054.77</v>
       </c>
+      <c r="E91" s="22">
+        <f>_xlfn.XLOOKUP(A91, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>6054.77</v>
+      </c>
+      <c r="F91" s="21">
+        <f>_xlfn.XLOOKUP(A91, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J91" t="s">
         <v>1699</v>
       </c>
@@ -20172,6 +20922,14 @@
       <c r="D92" s="18">
         <v>43512.46</v>
       </c>
+      <c r="E92" s="22">
+        <f>_xlfn.XLOOKUP(A92, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>43512.46</v>
+      </c>
+      <c r="F92" s="21">
+        <f>_xlfn.XLOOKUP(A92, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J92" t="s">
         <v>1701</v>
       </c>
@@ -20201,6 +20959,14 @@
       <c r="D93" s="18">
         <v>34050.42</v>
       </c>
+      <c r="E93" s="22">
+        <f>_xlfn.XLOOKUP(A93, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>34050.42</v>
+      </c>
+      <c r="F93" s="21">
+        <f>_xlfn.XLOOKUP(A93, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J93" t="s">
         <v>1703</v>
       </c>
@@ -20230,6 +20996,14 @@
       <c r="D94" s="18">
         <v>39370.720000000001</v>
       </c>
+      <c r="E94" s="22">
+        <f>_xlfn.XLOOKUP(A94, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>39370.720000000001</v>
+      </c>
+      <c r="F94" s="21">
+        <f>_xlfn.XLOOKUP(A94, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J94" t="s">
         <v>1705</v>
       </c>
@@ -20259,6 +21033,14 @@
       <c r="D95" s="18">
         <v>18577.43</v>
       </c>
+      <c r="E95" s="22">
+        <f>_xlfn.XLOOKUP(A95, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>18577.43</v>
+      </c>
+      <c r="F95" s="21">
+        <f>_xlfn.XLOOKUP(A95, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J95" t="s">
         <v>1707</v>
       </c>
@@ -20288,6 +21070,14 @@
       <c r="D96" s="18">
         <v>44332.38</v>
       </c>
+      <c r="E96" s="22">
+        <f>_xlfn.XLOOKUP(A96, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>44332.38</v>
+      </c>
+      <c r="F96" s="21">
+        <f>_xlfn.XLOOKUP(A96, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J96" t="s">
         <v>1710</v>
       </c>
@@ -20317,6 +21107,14 @@
       <c r="D97" s="18">
         <v>6646.34</v>
       </c>
+      <c r="E97" s="22">
+        <f>_xlfn.XLOOKUP(A97, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>6646.34</v>
+      </c>
+      <c r="F97" s="21">
+        <f>_xlfn.XLOOKUP(A97, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J97" t="s">
         <v>1713</v>
       </c>
@@ -20346,6 +21144,14 @@
       <c r="D98" s="18">
         <v>34450.94</v>
       </c>
+      <c r="E98" s="22" t="str">
+        <f>_xlfn.XLOOKUP(A98, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>NOT IN LEDGER</v>
+      </c>
+      <c r="F98" s="21" t="str">
+        <f>_xlfn.XLOOKUP(A98, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>DATE NOT FOUND</v>
+      </c>
       <c r="J98" t="s">
         <v>1716</v>
       </c>
@@ -20375,6 +21181,14 @@
       <c r="D99" s="18">
         <v>12407.34</v>
       </c>
+      <c r="E99" s="22">
+        <f>_xlfn.XLOOKUP(A99, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>12407.34</v>
+      </c>
+      <c r="F99" s="21">
+        <f>_xlfn.XLOOKUP(A99, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J99" t="s">
         <v>1720</v>
       </c>
@@ -20404,6 +21218,14 @@
       <c r="D100" s="18">
         <v>423.41</v>
       </c>
+      <c r="E100" s="22">
+        <f>_xlfn.XLOOKUP(A100, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>423.41</v>
+      </c>
+      <c r="F100" s="21">
+        <f>_xlfn.XLOOKUP(A100, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J100" t="s">
         <v>1722</v>
       </c>
@@ -20433,6 +21255,14 @@
       <c r="D101" s="18">
         <v>6022.57</v>
       </c>
+      <c r="E101" s="22">
+        <f>_xlfn.XLOOKUP(A101, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>6022.57</v>
+      </c>
+      <c r="F101" s="21">
+        <f>_xlfn.XLOOKUP(A101, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J101" t="s">
         <v>1724</v>
       </c>
@@ -20462,6 +21292,14 @@
       <c r="D102" s="18">
         <v>9873.73</v>
       </c>
+      <c r="E102" s="22">
+        <f>_xlfn.XLOOKUP(A102, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>9873.73</v>
+      </c>
+      <c r="F102" s="21">
+        <f>_xlfn.XLOOKUP(A102, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J102" t="s">
         <v>1726</v>
       </c>
@@ -20491,6 +21329,14 @@
       <c r="D103" s="18">
         <v>36699.74</v>
       </c>
+      <c r="E103" s="22">
+        <f>_xlfn.XLOOKUP(A103, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>36699.74</v>
+      </c>
+      <c r="F103" s="21">
+        <f>_xlfn.XLOOKUP(A103, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J103" t="s">
         <v>1728</v>
       </c>
@@ -20520,6 +21366,14 @@
       <c r="D104" s="18">
         <v>18301.89</v>
       </c>
+      <c r="E104" s="22">
+        <f>_xlfn.XLOOKUP(A104, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>18301.89</v>
+      </c>
+      <c r="F104" s="21">
+        <f>_xlfn.XLOOKUP(A104, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J104" t="s">
         <v>1730</v>
       </c>
@@ -20549,6 +21403,14 @@
       <c r="D105" s="18">
         <v>23266.959999999999</v>
       </c>
+      <c r="E105" s="22">
+        <f>_xlfn.XLOOKUP(A105, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>23266.959999999999</v>
+      </c>
+      <c r="F105" s="21">
+        <f>_xlfn.XLOOKUP(A105, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J105" t="s">
         <v>1732</v>
       </c>
@@ -20578,6 +21440,14 @@
       <c r="D106" s="18">
         <v>29548.53</v>
       </c>
+      <c r="E106" s="22">
+        <f>_xlfn.XLOOKUP(A106, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>29548.53</v>
+      </c>
+      <c r="F106" s="21">
+        <f>_xlfn.XLOOKUP(A106, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46095</v>
+      </c>
       <c r="J106" t="s">
         <v>1734</v>
       </c>
@@ -20607,6 +21477,14 @@
       <c r="D107" s="18">
         <v>13030.78</v>
       </c>
+      <c r="E107" s="22">
+        <f>_xlfn.XLOOKUP(A107, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>13030.78</v>
+      </c>
+      <c r="F107" s="21">
+        <f>_xlfn.XLOOKUP(A107, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J107" t="s">
         <v>1737</v>
       </c>
@@ -20636,6 +21514,14 @@
       <c r="D108" s="18">
         <v>30735.200000000001</v>
       </c>
+      <c r="E108" s="22">
+        <f>_xlfn.XLOOKUP(A108, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>30735.200000000001</v>
+      </c>
+      <c r="F108" s="21">
+        <f>_xlfn.XLOOKUP(A108, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46098</v>
+      </c>
       <c r="J108" t="s">
         <v>1739</v>
       </c>
@@ -20665,6 +21551,14 @@
       <c r="D109" s="18">
         <v>32317.56</v>
       </c>
+      <c r="E109" s="22">
+        <f>_xlfn.XLOOKUP(A109, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>32317.56</v>
+      </c>
+      <c r="F109" s="21">
+        <f>_xlfn.XLOOKUP(A109, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46100</v>
+      </c>
       <c r="J109" t="s">
         <v>1741</v>
       </c>
@@ -20694,6 +21588,14 @@
       <c r="D110" s="18">
         <v>44245.38</v>
       </c>
+      <c r="E110" s="22">
+        <f>_xlfn.XLOOKUP(A110, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>44245.38</v>
+      </c>
+      <c r="F110" s="21">
+        <f>_xlfn.XLOOKUP(A110, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46102</v>
+      </c>
       <c r="J110" t="s">
         <v>1743</v>
       </c>
@@ -20723,6 +21625,14 @@
       <c r="D111" s="18">
         <v>24261.89</v>
       </c>
+      <c r="E111" s="22">
+        <f>_xlfn.XLOOKUP(A111, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>24261.89</v>
+      </c>
+      <c r="F111" s="21">
+        <f>_xlfn.XLOOKUP(A111, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46104</v>
+      </c>
       <c r="J111" t="s">
         <v>1745</v>
       </c>
@@ -20752,6 +21662,14 @@
       <c r="D112" s="18">
         <v>41089.910000000003</v>
       </c>
+      <c r="E112" s="22">
+        <f>_xlfn.XLOOKUP(A112, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>41089.910000000003</v>
+      </c>
+      <c r="F112" s="21">
+        <f>_xlfn.XLOOKUP(A112, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46106</v>
+      </c>
       <c r="J112" t="s">
         <v>1748</v>
       </c>
@@ -20781,6 +21699,14 @@
       <c r="D113" s="18">
         <v>46460.14</v>
       </c>
+      <c r="E113" s="22">
+        <f>_xlfn.XLOOKUP(A113, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>46460.14</v>
+      </c>
+      <c r="F113" s="21">
+        <f>_xlfn.XLOOKUP(A113, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46108</v>
+      </c>
       <c r="J113" t="s">
         <v>1751</v>
       </c>
@@ -20810,6 +21736,14 @@
       <c r="D114" s="18">
         <v>36964.76</v>
       </c>
+      <c r="E114" s="22">
+        <f>_xlfn.XLOOKUP(A114, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>36964.76</v>
+      </c>
+      <c r="F114" s="21">
+        <f>_xlfn.XLOOKUP(A114, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46082</v>
+      </c>
       <c r="J114" t="s">
         <v>1753</v>
       </c>
@@ -20839,6 +21773,14 @@
       <c r="D115" s="18">
         <v>20361.91</v>
       </c>
+      <c r="E115" s="22">
+        <f>_xlfn.XLOOKUP(A115, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>20361.91</v>
+      </c>
+      <c r="F115" s="21">
+        <f>_xlfn.XLOOKUP(A115, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46084</v>
+      </c>
       <c r="J115" t="s">
         <v>1755</v>
       </c>
@@ -20868,6 +21810,14 @@
       <c r="D116" s="18">
         <v>13237.04</v>
       </c>
+      <c r="E116" s="22">
+        <f>_xlfn.XLOOKUP(A116, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>13237.04</v>
+      </c>
+      <c r="F116" s="21">
+        <f>_xlfn.XLOOKUP(A116, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46086</v>
+      </c>
       <c r="J116" t="s">
         <v>1757</v>
       </c>
@@ -20897,6 +21847,14 @@
       <c r="D117" s="18">
         <v>4916.7</v>
       </c>
+      <c r="E117" s="22">
+        <f>_xlfn.XLOOKUP(A117, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>4916.7</v>
+      </c>
+      <c r="F117" s="21">
+        <f>_xlfn.XLOOKUP(A117, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46088</v>
+      </c>
       <c r="J117" t="s">
         <v>1759</v>
       </c>
@@ -20926,6 +21884,14 @@
       <c r="D118" s="18">
         <v>39931.53</v>
       </c>
+      <c r="E118" s="22">
+        <f>_xlfn.XLOOKUP(A118, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>39931.53</v>
+      </c>
+      <c r="F118" s="21">
+        <f>_xlfn.XLOOKUP(A118, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46090</v>
+      </c>
       <c r="J118" t="s">
         <v>1761</v>
       </c>
@@ -20955,6 +21921,14 @@
       <c r="D119" s="18">
         <v>6438.4</v>
       </c>
+      <c r="E119" s="22">
+        <f>_xlfn.XLOOKUP(A119, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>6438.4</v>
+      </c>
+      <c r="F119" s="21">
+        <f>_xlfn.XLOOKUP(A119, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46092</v>
+      </c>
       <c r="J119" t="s">
         <v>1763</v>
       </c>
@@ -20984,6 +21958,14 @@
       <c r="D120" s="18">
         <v>26966.74</v>
       </c>
+      <c r="E120" s="22">
+        <f>_xlfn.XLOOKUP(A120, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>26966.74</v>
+      </c>
+      <c r="F120" s="21">
+        <f>_xlfn.XLOOKUP(A120, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46094</v>
+      </c>
       <c r="J120" t="s">
         <v>1765</v>
       </c>
@@ -21013,6 +21995,14 @@
       <c r="D121" s="18">
         <v>21925.19</v>
       </c>
+      <c r="E121" s="22">
+        <f>_xlfn.XLOOKUP(A121, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</f>
+        <v>21925.19</v>
+      </c>
+      <c r="F121" s="21">
+        <f>_xlfn.XLOOKUP(A121, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
+        <v>46096</v>
+      </c>
       <c r="J121" t="s">
         <v>1767</v>
       </c>
@@ -21048,9 +22038,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45411,25 +46402,25 @@
       <c r="B6" s="7">
         <v>20937</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" s="7">
         <v>55846</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" s="7">
         <v>32272</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6">
         <v>2</v>
       </c>
       <c r="H6" s="7">
         <v>109055</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6">
         <v>12</v>
       </c>
     </row>
@@ -45440,25 +46431,25 @@
       <c r="B7" s="7">
         <v>28417</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7">
         <v>5</v>
       </c>
       <c r="D7" s="7">
         <v>33726</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" s="7">
         <v>21386</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" s="7">
         <v>83529</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7">
         <v>13</v>
       </c>
     </row>
@@ -45469,25 +46460,25 @@
       <c r="B8" s="7">
         <v>19998</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" s="7">
         <v>4905</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" s="7">
         <v>26576</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8">
         <v>7</v>
       </c>
       <c r="H8" s="7">
         <v>51479</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8">
         <v>12</v>
       </c>
     </row>
@@ -45498,25 +46489,25 @@
       <c r="B9" s="7">
         <v>69352</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9">
         <v>12</v>
       </c>
       <c r="D9" s="7">
         <v>94477</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9">
         <v>13</v>
       </c>
       <c r="F9" s="7">
         <v>80234</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9">
         <v>12</v>
       </c>
       <c r="H9" s="7">
         <v>244063</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9">
         <v>37</v>
       </c>
     </row>
@@ -45777,7 +46768,7 @@
       <c r="B7" s="18">
         <v>12500</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" s="18">
@@ -45789,7 +46780,7 @@
       <c r="F7" s="18">
         <v>15900</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7">
         <v>1</v>
       </c>
       <c r="H7" s="18">
@@ -45799,13 +46790,12 @@
         <v>15900</v>
       </c>
       <c r="J7" s="18"/>
-      <c r="K7" s="29"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18">
         <v>28400</v>
       </c>
-      <c r="O7" s="29">
+      <c r="O7">
         <v>2</v>
       </c>
       <c r="P7" s="18">
@@ -45822,7 +46812,7 @@
       <c r="B8" s="18">
         <v>23836</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" s="18">
@@ -45834,7 +46824,7 @@
       <c r="F8" s="18">
         <v>10891</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8">
         <v>4</v>
       </c>
       <c r="H8" s="18">
@@ -45846,7 +46836,7 @@
       <c r="J8" s="18">
         <v>26673</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8">
         <v>7</v>
       </c>
       <c r="L8" s="18">
@@ -45858,7 +46848,7 @@
       <c r="N8" s="18">
         <v>61400</v>
       </c>
-      <c r="O8" s="29">
+      <c r="O8">
         <v>15</v>
       </c>
       <c r="P8" s="18">
@@ -45875,7 +46865,7 @@
       <c r="B9" s="18">
         <v>18400</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" s="18">
@@ -45885,17 +46875,15 @@
         <v>18400</v>
       </c>
       <c r="F9" s="18"/>
-      <c r="G9" s="29"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
-      <c r="K9" s="29"/>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="18">
         <v>18400</v>
       </c>
-      <c r="O9" s="29">
+      <c r="O9">
         <v>1</v>
       </c>
       <c r="P9" s="18">
@@ -45912,7 +46900,7 @@
       <c r="B10" s="18">
         <v>30785</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10">
         <v>5</v>
       </c>
       <c r="D10" s="18">
@@ -45924,7 +46912,7 @@
       <c r="F10" s="18">
         <v>16138</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" s="18">
@@ -45936,7 +46924,7 @@
       <c r="J10" s="18">
         <v>30821</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10">
         <v>5</v>
       </c>
       <c r="L10" s="18">
@@ -45948,7 +46936,7 @@
       <c r="N10" s="18">
         <v>77744</v>
       </c>
-      <c r="O10" s="29">
+      <c r="O10">
         <v>14</v>
       </c>
       <c r="P10" s="18">
@@ -45965,7 +46953,7 @@
       <c r="B11" s="18">
         <v>10000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" s="18">
@@ -45975,17 +46963,15 @@
         <v>10000</v>
       </c>
       <c r="F11" s="18"/>
-      <c r="G11" s="29"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
-      <c r="K11" s="29"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="18">
         <v>10000</v>
       </c>
-      <c r="O11" s="29">
+      <c r="O11">
         <v>1</v>
       </c>
       <c r="P11" s="18">
@@ -46002,7 +46988,7 @@
       <c r="B12" s="18">
         <v>20480</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" s="18">
@@ -46014,7 +47000,7 @@
       <c r="F12" s="18">
         <v>57769</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" s="18">
@@ -46026,7 +47012,7 @@
       <c r="J12" s="18">
         <v>40877</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12">
         <v>5</v>
       </c>
       <c r="L12" s="18">
@@ -46038,7 +47024,7 @@
       <c r="N12" s="18">
         <v>119126</v>
       </c>
-      <c r="O12" s="29">
+      <c r="O12">
         <v>14</v>
       </c>
       <c r="P12" s="18">
@@ -46053,13 +47039,12 @@
         <v>1143</v>
       </c>
       <c r="B13" s="18"/>
-      <c r="C13" s="29"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18">
         <v>26750</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" s="18">
@@ -46069,13 +47054,12 @@
         <v>26750</v>
       </c>
       <c r="J13" s="18"/>
-      <c r="K13" s="29"/>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
       <c r="N13" s="18">
         <v>26750</v>
       </c>
-      <c r="O13" s="29">
+      <c r="O13">
         <v>1</v>
       </c>
       <c r="P13" s="18">
@@ -46090,13 +47074,12 @@
         <v>1151</v>
       </c>
       <c r="B14" s="18"/>
-      <c r="C14" s="29"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18">
         <v>58050</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14">
         <v>6</v>
       </c>
       <c r="H14" s="18">
@@ -46106,13 +47089,12 @@
         <v>9675</v>
       </c>
       <c r="J14" s="18"/>
-      <c r="K14" s="29"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18">
         <v>58050</v>
       </c>
-      <c r="O14" s="29">
+      <c r="O14">
         <v>6</v>
       </c>
       <c r="P14" s="18">
@@ -46129,7 +47111,7 @@
       <c r="B15" s="18">
         <v>38802</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15">
         <v>4</v>
       </c>
       <c r="D15" s="18">
@@ -46141,7 +47123,7 @@
       <c r="F15" s="18">
         <v>20567</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" s="18">
@@ -46153,7 +47135,7 @@
       <c r="J15" s="18">
         <v>30852</v>
       </c>
-      <c r="K15" s="29">
+      <c r="K15">
         <v>6</v>
       </c>
       <c r="L15" s="18">
@@ -46165,7 +47147,7 @@
       <c r="N15" s="18">
         <v>90221</v>
       </c>
-      <c r="O15" s="29">
+      <c r="O15">
         <v>15</v>
       </c>
       <c r="P15" s="18">
@@ -46182,7 +47164,7 @@
       <c r="B16" s="18">
         <v>154803</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16">
         <v>20</v>
       </c>
       <c r="D16" s="18">
@@ -46194,7 +47176,7 @@
       <c r="F16" s="18">
         <v>206065</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16">
         <v>26</v>
       </c>
       <c r="H16" s="18">
@@ -46206,7 +47188,7 @@
       <c r="J16" s="18">
         <v>129223</v>
       </c>
-      <c r="K16" s="29">
+      <c r="K16">
         <v>23</v>
       </c>
       <c r="L16" s="18">
@@ -46218,7 +47200,7 @@
       <c r="N16" s="18">
         <v>490091</v>
       </c>
-      <c r="O16" s="29">
+      <c r="O16">
         <v>69</v>
       </c>
       <c r="P16" s="18">

--- a/Sheets/ops-primer-live.xlsx
+++ b/Sheets/ops-primer-live.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanDeLaCruz\Documents\Revature\excel-primer\demo\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D531CFC-D113-4309-8A96-5454F28C35B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9560E019-98F0-4E18-802A-06E8449778CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="12900" windowWidth="23256" windowHeight="12456" tabRatio="549" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9913" uniqueCount="2365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9916" uniqueCount="2367">
   <si>
     <t>Ops Analyst Excel Primer - two days, one workbook</t>
   </si>
@@ -7179,6 +7179,12 @@
   </si>
   <si>
     <t>ledger_date</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>pending</t>
   </si>
 </sst>
 </file>
@@ -7346,10 +7352,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -7422,6 +7425,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -16575,7 +16587,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}" name="tblEng01" displayName="tblEng01" ref="A1:M41" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}" name="tblEng01" displayName="tblEng01" ref="A1:M41" headerRowDxfId="13">
   <autoFilter ref="A1:M41" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J41">
     <sortCondition ref="A1:A41"/>
@@ -16586,10 +16598,10 @@
     <tableColumn id="3" xr3:uid="{B8BB6B56-8344-499F-BAB4-84715457D6EF}" name="engagement_name"/>
     <tableColumn id="4" xr3:uid="{039EFC86-5137-4E51-91AE-860C7AF50C24}" name="service_line"/>
     <tableColumn id="5" xr3:uid="{6FF6A3D2-17A1-4FD9-AEAA-C1032E532018}" name="manager"/>
-    <tableColumn id="6" xr3:uid="{75A6260E-7674-4FE9-BA83-0D2F7F16F9B5}" name="start_date" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{BEA051CC-DB8F-401A-9BD4-F8DA896A9836}" name="end_date" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{A133F6EB-61F1-447E-9563-209E1FE38970}" name="budget" totalsRowFunction="sum" dataDxfId="11" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{19614B11-9DC3-43E2-AC6B-5229754C7678}" name="actual_cost" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{75A6260E-7674-4FE9-BA83-0D2F7F16F9B5}" name="start_date" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{BEA051CC-DB8F-401A-9BD4-F8DA896A9836}" name="end_date" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{A133F6EB-61F1-447E-9563-209E1FE38970}" name="budget" totalsRowFunction="sum" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{19614B11-9DC3-43E2-AC6B-5229754C7678}" name="actual_cost" dataDxfId="9" dataCellStyle="Comma"/>
     <tableColumn id="10" xr3:uid="{7B805801-F707-4199-B930-DC0ABE2A33AF}" name="status" totalsRowFunction="count"/>
     <tableColumn id="11" xr3:uid="{3950F076-67D4-48CF-AEED-6EB579504530}" name="variance"/>
     <tableColumn id="12" xr3:uid="{B4D02EB1-68B9-4311-8D42-EEBDC2CC34B1}" name="margin_pct"/>
@@ -16613,13 +16625,13 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="budget"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="actual_cost"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="variance" dataDxfId="9">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="variance" dataDxfId="8">
       <calculatedColumnFormula>H2-I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="margin_pct" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="margin_pct" dataDxfId="7">
       <calculatedColumnFormula>K2/H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="budget_with_uplift" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="budget_with_uplift" dataDxfId="6">
       <calculatedColumnFormula>H2*(1+$T$2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16641,23 +16653,23 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="budget"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="actual_cost"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="variance" dataDxfId="6">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="variance" dataDxfId="5">
       <calculatedColumnFormula>IF(ISBLANK(I2), "NO COST YET", H2-I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="margin_pct" dataDxfId="5">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="margin_pct" dataDxfId="4">
       <calculatedColumnFormula>IF(ISBLANK(I2), "NO COST YET", K2/H2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="budget_with_uplift"/>
-    <tableColumn id="14" xr3:uid="{6ADA16E7-AD66-40BD-A05E-BB51EC772142}" name="client_name" dataDxfId="4">
+    <tableColumn id="14" xr3:uid="{6ADA16E7-AD66-40BD-A05E-BB51EC772142}" name="client_name" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, tblClients[client_id], tblClients[client_name], "CHECK CLIENT ID")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C3B845C8-E030-43EF-9659-5C91666A6672}" name="risk_rating" dataDxfId="3">
+    <tableColumn id="15" xr3:uid="{C3B845C8-E030-43EF-9659-5C91666A6672}" name="risk_rating" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, tblClients[client_id], tblClients[risk_rating], "No Risk Rating")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4A82E2C7-ECC2-4171-997E-328DE1C8B926}" name="id_count" dataDxfId="2">
+    <tableColumn id="16" xr3:uid="{4A82E2C7-ECC2-4171-997E-328DE1C8B926}" name="id_count" dataDxfId="1">
       <calculatedColumnFormula>COUNTIF(tblEng03[engagement_id], A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7CEF5B5F-12BC-4339-9D42-68F689835FEF}" name="id_ok" dataDxfId="1">
+    <tableColumn id="17" xr3:uid="{7CEF5B5F-12BC-4339-9D42-68F689835FEF}" name="id_ok" dataDxfId="0">
       <calculatedColumnFormula>IF(LEN(A2)=8, "OK", "CHECK LENGTH")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16709,9 +16721,9 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tblBank" displayName="tblBank" ref="A1:F121">
-  <autoFilter ref="A1:F121" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tblBank" displayName="tblBank" ref="A1:H121">
+  <autoFilter ref="A1:H121" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="bank_ref"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="post_date"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="description"/>
@@ -16719,8 +16731,14 @@
     <tableColumn id="5" xr3:uid="{ED33286F-F1AA-46F5-B515-FFC040B420F4}" name="ledger_amount" dataCellStyle="Comma">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[amount], "NOT IN LEDGER")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A9B9FD23-BE98-417A-8BA4-1F1708AF698D}" name="ledger_date" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{A9B9FD23-BE98-417A-8BA4-1F1708AF698D}" name="ledger_date" dataDxfId="16">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{AE76DD12-19A6-4FA5-AB8E-4ACBB9017348}" name="delta" dataDxfId="15">
+      <calculatedColumnFormula>IFERROR(D2-E2, "ERROR")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{67D977EF-6545-4D4B-908B-E04A483FEED4}" name="status" dataDxfId="14">
+      <calculatedColumnFormula>IF(E2="NOT IN LEDGER", "MISSING IN LEDGER", IF(ABS(G2)&gt;=0.01, "AMOUNT DIFFERS", IF(F2&lt;&gt;B2, "DATE DIFFERS", "OK")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -17308,7 +17326,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AA122"/>
+  <dimension ref="A1:AA126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -17316,7 +17334,7 @@
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="17.140625" style="22" customWidth="1"/>
-    <col min="6" max="6" width="13" style="21" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="21" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="2" customWidth="1"/>
@@ -17356,6 +17374,12 @@
       <c r="F1" s="21" t="s">
         <v>2364</v>
       </c>
+      <c r="G1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
       <c r="J1" t="s">
         <v>1372</v>
       </c>
@@ -17420,6 +17444,14 @@
         <f>_xlfn.XLOOKUP(A2, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G2">
+        <f t="shared" ref="G2:G33" si="0">IFERROR(D2-E2, "ERROR")</f>
+        <v>0</v>
+      </c>
+      <c r="H2" t="str">
+        <f t="shared" ref="H2:H33" si="1">IF(E2="NOT IN LEDGER", "MISSING IN LEDGER", IF(ABS(G2)&gt;=0.01, "AMOUNT DIFFERS", IF(F2&lt;&gt;B2, "DATE DIFFERS", "OK")))</f>
+        <v>OK</v>
+      </c>
       <c r="J2" t="s">
         <v>1386</v>
       </c>
@@ -17435,14 +17467,18 @@
       <c r="N2" s="18">
         <v>11671.47</v>
       </c>
-      <c r="R2" s="19"/>
+      <c r="R2" s="19">
+        <v>1</v>
+      </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
       <c r="U2" s="19"/>
       <c r="V2" s="19"/>
       <c r="W2" s="19"/>
       <c r="X2" s="19"/>
-      <c r="Y2" s="19"/>
+      <c r="Y2" s="19" t="s">
+        <v>2366</v>
+      </c>
       <c r="AA2" s="4" t="s">
         <v>1388</v>
       </c>
@@ -17468,6 +17504,14 @@
         <f>_xlfn.XLOOKUP(A3, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G3">
+        <f>IFERROR(D3-E3, "ERROR")</f>
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J3" t="s">
         <v>1391</v>
       </c>
@@ -17483,7 +17527,9 @@
       <c r="N3" s="18">
         <v>8253.75</v>
       </c>
-      <c r="R3" s="19"/>
+      <c r="R3" s="19">
+        <v>2</v>
+      </c>
       <c r="S3" s="19"/>
       <c r="T3" s="19"/>
       <c r="U3" s="19"/>
@@ -17516,6 +17562,14 @@
         <f>_xlfn.XLOOKUP(A4, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J4" t="s">
         <v>1397</v>
       </c>
@@ -17531,7 +17585,9 @@
       <c r="N4" s="18">
         <v>12426.71</v>
       </c>
-      <c r="R4" s="19"/>
+      <c r="R4" s="19">
+        <v>3</v>
+      </c>
       <c r="S4" s="19"/>
       <c r="T4" s="19"/>
       <c r="U4" s="19"/>
@@ -17564,6 +17620,14 @@
         <f>_xlfn.XLOOKUP(A5, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J5" t="s">
         <v>1403</v>
       </c>
@@ -17579,7 +17643,9 @@
       <c r="N5" s="18">
         <v>26699.41</v>
       </c>
-      <c r="R5" s="19"/>
+      <c r="R5" s="19">
+        <v>4</v>
+      </c>
       <c r="S5" s="19"/>
       <c r="T5" s="19"/>
       <c r="U5" s="19"/>
@@ -17612,6 +17678,14 @@
         <f>_xlfn.XLOOKUP(A6, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J6" t="s">
         <v>1408</v>
       </c>
@@ -17657,6 +17731,14 @@
       <c r="F7" s="21">
         <f>_xlfn.XLOOKUP(A7, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
       </c>
       <c r="J7" t="s">
         <v>1412</v>
@@ -17706,6 +17788,14 @@
         <f>_xlfn.XLOOKUP(A8, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J8" t="s">
         <v>1417</v>
       </c>
@@ -17754,6 +17844,14 @@
         <f>_xlfn.XLOOKUP(A9, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J9" t="s">
         <v>1422</v>
       </c>
@@ -17802,6 +17900,14 @@
         <f>_xlfn.XLOOKUP(A10, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J10" t="s">
         <v>1427</v>
       </c>
@@ -17850,6 +17956,14 @@
         <f>_xlfn.XLOOKUP(A11, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J11" t="s">
         <v>1432</v>
       </c>
@@ -17898,6 +18012,14 @@
         <f>_xlfn.XLOOKUP(A12, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J12" t="s">
         <v>1437</v>
       </c>
@@ -17943,6 +18065,14 @@
       <c r="F13" s="21">
         <f>_xlfn.XLOOKUP(A13, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
       </c>
       <c r="J13" t="s">
         <v>1442</v>
@@ -17992,6 +18122,14 @@
         <f>_xlfn.XLOOKUP(A14, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J14" t="s">
         <v>1448</v>
       </c>
@@ -18040,6 +18178,14 @@
         <f>_xlfn.XLOOKUP(A15, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J15" t="s">
         <v>1453</v>
       </c>
@@ -18088,6 +18234,14 @@
         <f>_xlfn.XLOOKUP(A16, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J16" t="s">
         <v>1457</v>
       </c>
@@ -18134,6 +18288,14 @@
         <f>_xlfn.XLOOKUP(A17, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J17" t="s">
         <v>1460</v>
       </c>
@@ -18174,6 +18336,14 @@
         <f>_xlfn.XLOOKUP(A18, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>DATE NOT FOUND</v>
       </c>
+      <c r="G18" t="str">
+        <f>IFERROR(D18-E18, "ERROR")</f>
+        <v>ERROR</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>MISSING IN LEDGER</v>
+      </c>
       <c r="J18" t="s">
         <v>1465</v>
       </c>
@@ -18214,6 +18384,14 @@
         <f>_xlfn.XLOOKUP(A19, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J19" t="s">
         <v>1470</v>
       </c>
@@ -18254,6 +18432,14 @@
         <f>_xlfn.XLOOKUP(A20, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J20" t="s">
         <v>1474</v>
       </c>
@@ -18269,18 +18455,9 @@
       <c r="N20" s="18">
         <v>13578.64</v>
       </c>
-      <c r="R20" s="18">
-        <f>SUM(tblBank[amount])</f>
-        <v>2755208.6699999995</v>
-      </c>
-      <c r="S20" s="18">
-        <f>SUM(tblLedger[amount])</f>
-        <v>2720606.96</v>
-      </c>
-      <c r="T20" s="18">
-        <f>R20-S20</f>
-        <v>34601.709999999497</v>
-      </c>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -18303,6 +18480,14 @@
         <f>_xlfn.XLOOKUP(A21, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J21" t="s">
         <v>1478</v>
       </c>
@@ -18340,6 +18525,14 @@
         <f>_xlfn.XLOOKUP(A22, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J22" t="s">
         <v>1482</v>
       </c>
@@ -18377,6 +18570,14 @@
         <f>_xlfn.XLOOKUP(A23, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J23" t="s">
         <v>1486</v>
       </c>
@@ -18414,6 +18615,14 @@
         <f>_xlfn.XLOOKUP(A24, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J24" t="s">
         <v>1490</v>
       </c>
@@ -18451,6 +18660,14 @@
         <f>_xlfn.XLOOKUP(A25, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J25" t="s">
         <v>1494</v>
       </c>
@@ -18488,6 +18705,14 @@
         <f>_xlfn.XLOOKUP(A26, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J26" t="s">
         <v>1498</v>
       </c>
@@ -18525,6 +18750,14 @@
         <f>_xlfn.XLOOKUP(A27, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J27" t="s">
         <v>1502</v>
       </c>
@@ -18562,6 +18795,14 @@
         <f>_xlfn.XLOOKUP(A28, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J28" t="s">
         <v>1505</v>
       </c>
@@ -18599,6 +18840,14 @@
         <f>_xlfn.XLOOKUP(A29, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J29" t="s">
         <v>1508</v>
       </c>
@@ -18636,6 +18885,14 @@
         <f>_xlfn.XLOOKUP(A30, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J30" t="s">
         <v>1511</v>
       </c>
@@ -18673,6 +18930,14 @@
         <f>_xlfn.XLOOKUP(A31, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J31" t="s">
         <v>1514</v>
       </c>
@@ -18710,6 +18975,14 @@
         <f>_xlfn.XLOOKUP(A32, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J32" t="s">
         <v>1517</v>
       </c>
@@ -18747,6 +19020,14 @@
         <f>_xlfn.XLOOKUP(A33, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v>OK</v>
+      </c>
       <c r="J33" t="s">
         <v>1520</v>
       </c>
@@ -18784,6 +19065,14 @@
         <f>_xlfn.XLOOKUP(A34, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G34">
+        <f t="shared" ref="G34:G65" si="2">IFERROR(D34-E34, "ERROR")</f>
+        <v>-450</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" ref="H34:H65" si="3">IF(E34="NOT IN LEDGER", "MISSING IN LEDGER", IF(ABS(G34)&gt;=0.01, "AMOUNT DIFFERS", IF(F34&lt;&gt;B34, "DATE DIFFERS", "OK")))</f>
+        <v>AMOUNT DIFFERS</v>
+      </c>
       <c r="J34" t="s">
         <v>1524</v>
       </c>
@@ -18821,6 +19110,14 @@
         <f>_xlfn.XLOOKUP(A35, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J35" t="s">
         <v>1528</v>
       </c>
@@ -18858,6 +19155,14 @@
         <f>_xlfn.XLOOKUP(A36, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J36" t="s">
         <v>1532</v>
       </c>
@@ -18895,6 +19200,14 @@
         <f>_xlfn.XLOOKUP(A37, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J37" t="s">
         <v>1536</v>
       </c>
@@ -18932,6 +19245,14 @@
         <f>_xlfn.XLOOKUP(A38, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J38" t="s">
         <v>1539</v>
       </c>
@@ -18969,6 +19290,14 @@
         <f>_xlfn.XLOOKUP(A39, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J39" t="s">
         <v>1542</v>
       </c>
@@ -19006,6 +19335,14 @@
         <f>_xlfn.XLOOKUP(A40, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J40" t="s">
         <v>1545</v>
       </c>
@@ -19043,6 +19380,14 @@
         <f>_xlfn.XLOOKUP(A41, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J41" t="s">
         <v>1549</v>
       </c>
@@ -19080,6 +19425,14 @@
         <f>_xlfn.XLOOKUP(A42, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J42" t="s">
         <v>1553</v>
       </c>
@@ -19117,6 +19470,14 @@
         <f>_xlfn.XLOOKUP(A43, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J43" t="s">
         <v>1557</v>
       </c>
@@ -19154,6 +19515,14 @@
         <f>_xlfn.XLOOKUP(A44, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J44" t="s">
         <v>1560</v>
       </c>
@@ -19191,6 +19560,14 @@
         <f>_xlfn.XLOOKUP(A45, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J45" t="s">
         <v>1563</v>
       </c>
@@ -19228,6 +19605,14 @@
         <f>_xlfn.XLOOKUP(A46, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J46" t="s">
         <v>1566</v>
       </c>
@@ -19265,6 +19650,14 @@
         <f>_xlfn.XLOOKUP(A47, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J47" t="s">
         <v>1568</v>
       </c>
@@ -19302,6 +19695,14 @@
         <f>_xlfn.XLOOKUP(A48, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J48" t="s">
         <v>1570</v>
       </c>
@@ -19339,6 +19740,14 @@
         <f>_xlfn.XLOOKUP(A49, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J49" t="s">
         <v>1573</v>
       </c>
@@ -19376,6 +19785,14 @@
         <f>_xlfn.XLOOKUP(A50, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J50" t="s">
         <v>1576</v>
       </c>
@@ -19413,6 +19830,14 @@
         <f>_xlfn.XLOOKUP(A51, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J51" t="s">
         <v>1580</v>
       </c>
@@ -19450,6 +19875,14 @@
         <f>_xlfn.XLOOKUP(A52, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J52" t="s">
         <v>1584</v>
       </c>
@@ -19487,6 +19920,14 @@
         <f>_xlfn.XLOOKUP(A53, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J53" t="s">
         <v>1588</v>
       </c>
@@ -19524,6 +19965,14 @@
         <f>_xlfn.XLOOKUP(A54, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J54" t="s">
         <v>1592</v>
       </c>
@@ -19561,6 +20010,14 @@
         <f>_xlfn.XLOOKUP(A55, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J55" t="s">
         <v>1596</v>
       </c>
@@ -19598,6 +20055,14 @@
         <f>_xlfn.XLOOKUP(A56, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J56" t="s">
         <v>1600</v>
       </c>
@@ -19635,6 +20100,14 @@
         <f>_xlfn.XLOOKUP(A57, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J57" t="s">
         <v>1603</v>
       </c>
@@ -19672,6 +20145,14 @@
         <f>_xlfn.XLOOKUP(A58, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J58" t="s">
         <v>1605</v>
       </c>
@@ -19709,6 +20190,14 @@
         <f>_xlfn.XLOOKUP(A59, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>DATE NOT FOUND</v>
       </c>
+      <c r="G59" t="str">
+        <f t="shared" si="2"/>
+        <v>ERROR</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="3"/>
+        <v>MISSING IN LEDGER</v>
+      </c>
       <c r="J59" t="s">
         <v>1608</v>
       </c>
@@ -19746,6 +20235,14 @@
         <f>_xlfn.XLOOKUP(A60, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J60" t="s">
         <v>1610</v>
       </c>
@@ -19783,6 +20280,14 @@
         <f>_xlfn.XLOOKUP(A61, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J61" t="s">
         <v>1613</v>
       </c>
@@ -19820,6 +20325,14 @@
         <f>_xlfn.XLOOKUP(A62, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J62" t="s">
         <v>1616</v>
       </c>
@@ -19857,6 +20370,14 @@
         <f>_xlfn.XLOOKUP(A63, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J63" t="s">
         <v>1619</v>
       </c>
@@ -19894,6 +20415,14 @@
         <f>_xlfn.XLOOKUP(A64, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J64" t="s">
         <v>1622</v>
       </c>
@@ -19931,6 +20460,14 @@
         <f>_xlfn.XLOOKUP(A65, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
       <c r="J65" t="s">
         <v>1626</v>
       </c>
@@ -19968,6 +20505,14 @@
         <f>_xlfn.XLOOKUP(A66, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G66">
+        <f t="shared" ref="G66:G97" si="4">IFERROR(D66-E66, "ERROR")</f>
+        <v>0</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" ref="H66:H97" si="5">IF(E66="NOT IN LEDGER", "MISSING IN LEDGER", IF(ABS(G66)&gt;=0.01, "AMOUNT DIFFERS", IF(F66&lt;&gt;B66, "DATE DIFFERS", "OK")))</f>
+        <v>OK</v>
+      </c>
       <c r="J66" t="s">
         <v>1629</v>
       </c>
@@ -20005,6 +20550,14 @@
         <f>_xlfn.XLOOKUP(A67, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G67">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J67" t="s">
         <v>1632</v>
       </c>
@@ -20042,6 +20595,14 @@
         <f>_xlfn.XLOOKUP(A68, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J68" t="s">
         <v>1635</v>
       </c>
@@ -20079,6 +20640,14 @@
         <f>_xlfn.XLOOKUP(A69, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G69">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J69" t="s">
         <v>1638</v>
       </c>
@@ -20116,6 +20685,14 @@
         <f>_xlfn.XLOOKUP(A70, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J70" t="s">
         <v>1641</v>
       </c>
@@ -20153,6 +20730,14 @@
         <f>_xlfn.XLOOKUP(A71, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G71">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J71" t="s">
         <v>1645</v>
       </c>
@@ -20190,6 +20775,14 @@
         <f>_xlfn.XLOOKUP(A72, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G72">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="5"/>
+        <v>AMOUNT DIFFERS</v>
+      </c>
       <c r="J72" t="s">
         <v>1648</v>
       </c>
@@ -20227,6 +20820,14 @@
         <f>_xlfn.XLOOKUP(A73, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J73" t="s">
         <v>1651</v>
       </c>
@@ -20264,6 +20865,14 @@
         <f>_xlfn.XLOOKUP(A74, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G74">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J74" t="s">
         <v>1654</v>
       </c>
@@ -20301,6 +20910,14 @@
         <f>_xlfn.XLOOKUP(A75, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H75" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J75" t="s">
         <v>1656</v>
       </c>
@@ -20338,6 +20955,14 @@
         <f>_xlfn.XLOOKUP(A76, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H76" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J76" t="s">
         <v>1658</v>
       </c>
@@ -20375,6 +21000,14 @@
         <f>_xlfn.XLOOKUP(A77, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H77" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J77" t="s">
         <v>1660</v>
       </c>
@@ -20412,6 +21045,14 @@
         <f>_xlfn.XLOOKUP(A78, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J78" t="s">
         <v>1662</v>
       </c>
@@ -20449,6 +21090,14 @@
         <f>_xlfn.XLOOKUP(A79, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J79" t="s">
         <v>1664</v>
       </c>
@@ -20486,6 +21135,14 @@
         <f>_xlfn.XLOOKUP(A80, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J80" t="s">
         <v>1667</v>
       </c>
@@ -20523,6 +21180,14 @@
         <f>_xlfn.XLOOKUP(A81, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G81">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J81" t="s">
         <v>1671</v>
       </c>
@@ -20560,6 +21225,14 @@
         <f>_xlfn.XLOOKUP(A82, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G82">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J82" t="s">
         <v>1675</v>
       </c>
@@ -20597,6 +21270,14 @@
         <f>_xlfn.XLOOKUP(A83, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G83">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J83" t="s">
         <v>1679</v>
       </c>
@@ -20634,6 +21315,14 @@
         <f>_xlfn.XLOOKUP(A84, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G84">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H84" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J84" t="s">
         <v>1682</v>
       </c>
@@ -20671,6 +21360,14 @@
         <f>_xlfn.XLOOKUP(A85, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H85" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J85" t="s">
         <v>1685</v>
       </c>
@@ -20708,6 +21405,14 @@
         <f>_xlfn.XLOOKUP(A86, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J86" t="s">
         <v>1687</v>
       </c>
@@ -20745,6 +21450,14 @@
         <f>_xlfn.XLOOKUP(A87, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G87">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H87" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J87" t="s">
         <v>1689</v>
       </c>
@@ -20782,6 +21495,14 @@
         <f>_xlfn.XLOOKUP(A88, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G88">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H88" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J88" t="s">
         <v>1691</v>
       </c>
@@ -20819,6 +21540,14 @@
         <f>_xlfn.XLOOKUP(A89, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G89">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H89" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J89" t="s">
         <v>1693</v>
       </c>
@@ -20856,6 +21585,14 @@
         <f>_xlfn.XLOOKUP(A90, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G90">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H90" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J90" t="s">
         <v>1696</v>
       </c>
@@ -20893,6 +21630,14 @@
         <f>_xlfn.XLOOKUP(A91, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H91" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J91" t="s">
         <v>1699</v>
       </c>
@@ -20930,6 +21675,14 @@
         <f>_xlfn.XLOOKUP(A92, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G92">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H92" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J92" t="s">
         <v>1701</v>
       </c>
@@ -20967,6 +21720,14 @@
         <f>_xlfn.XLOOKUP(A93, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J93" t="s">
         <v>1703</v>
       </c>
@@ -21004,6 +21765,14 @@
         <f>_xlfn.XLOOKUP(A94, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J94" t="s">
         <v>1705</v>
       </c>
@@ -21041,6 +21810,14 @@
         <f>_xlfn.XLOOKUP(A95, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G95">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J95" t="s">
         <v>1707</v>
       </c>
@@ -21078,6 +21855,14 @@
         <f>_xlfn.XLOOKUP(A96, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G96">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H96" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J96" t="s">
         <v>1710</v>
       </c>
@@ -21115,6 +21900,14 @@
         <f>_xlfn.XLOOKUP(A97, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G97">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H97" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
       <c r="J97" t="s">
         <v>1713</v>
       </c>
@@ -21152,6 +21945,14 @@
         <f>_xlfn.XLOOKUP(A98, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>DATE NOT FOUND</v>
       </c>
+      <c r="G98" t="str">
+        <f t="shared" ref="G98:G121" si="6">IFERROR(D98-E98, "ERROR")</f>
+        <v>ERROR</v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" ref="H98:H121" si="7">IF(E98="NOT IN LEDGER", "MISSING IN LEDGER", IF(ABS(G98)&gt;=0.01, "AMOUNT DIFFERS", IF(F98&lt;&gt;B98, "DATE DIFFERS", "OK")))</f>
+        <v>MISSING IN LEDGER</v>
+      </c>
       <c r="J98" t="s">
         <v>1716</v>
       </c>
@@ -21189,6 +21990,14 @@
         <f>_xlfn.XLOOKUP(A99, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G99">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H99" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J99" t="s">
         <v>1720</v>
       </c>
@@ -21226,6 +22035,14 @@
         <f>_xlfn.XLOOKUP(A100, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G100">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J100" t="s">
         <v>1722</v>
       </c>
@@ -21263,6 +22080,14 @@
         <f>_xlfn.XLOOKUP(A101, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J101" t="s">
         <v>1724</v>
       </c>
@@ -21300,6 +22125,14 @@
         <f>_xlfn.XLOOKUP(A102, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J102" t="s">
         <v>1726</v>
       </c>
@@ -21337,6 +22170,14 @@
         <f>_xlfn.XLOOKUP(A103, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G103">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H103" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J103" t="s">
         <v>1728</v>
       </c>
@@ -21374,6 +22215,14 @@
         <f>_xlfn.XLOOKUP(A104, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G104">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H104" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J104" t="s">
         <v>1730</v>
       </c>
@@ -21411,6 +22260,14 @@
         <f>_xlfn.XLOOKUP(A105, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G105">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J105" t="s">
         <v>1732</v>
       </c>
@@ -21448,6 +22305,14 @@
         <f>_xlfn.XLOOKUP(A106, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46095</v>
       </c>
+      <c r="G106">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="7"/>
+        <v>DATE DIFFERS</v>
+      </c>
       <c r="J106" t="s">
         <v>1734</v>
       </c>
@@ -21485,6 +22350,14 @@
         <f>_xlfn.XLOOKUP(A107, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G107">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J107" t="s">
         <v>1737</v>
       </c>
@@ -21522,6 +22395,14 @@
         <f>_xlfn.XLOOKUP(A108, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46098</v>
       </c>
+      <c r="G108">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J108" t="s">
         <v>1739</v>
       </c>
@@ -21559,6 +22440,14 @@
         <f>_xlfn.XLOOKUP(A109, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46100</v>
       </c>
+      <c r="G109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H109" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J109" t="s">
         <v>1741</v>
       </c>
@@ -21596,6 +22485,14 @@
         <f>_xlfn.XLOOKUP(A110, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46102</v>
       </c>
+      <c r="G110">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H110" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J110" t="s">
         <v>1743</v>
       </c>
@@ -21633,6 +22530,14 @@
         <f>_xlfn.XLOOKUP(A111, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46104</v>
       </c>
+      <c r="G111">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H111" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J111" t="s">
         <v>1745</v>
       </c>
@@ -21670,6 +22575,14 @@
         <f>_xlfn.XLOOKUP(A112, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46106</v>
       </c>
+      <c r="G112">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H112" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J112" t="s">
         <v>1748</v>
       </c>
@@ -21707,6 +22620,14 @@
         <f>_xlfn.XLOOKUP(A113, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46108</v>
       </c>
+      <c r="G113">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H113" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J113" t="s">
         <v>1751</v>
       </c>
@@ -21744,6 +22665,14 @@
         <f>_xlfn.XLOOKUP(A114, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46082</v>
       </c>
+      <c r="G114">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H114" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J114" t="s">
         <v>1753</v>
       </c>
@@ -21781,6 +22710,14 @@
         <f>_xlfn.XLOOKUP(A115, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46084</v>
       </c>
+      <c r="G115">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H115" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J115" t="s">
         <v>1755</v>
       </c>
@@ -21818,6 +22755,14 @@
         <f>_xlfn.XLOOKUP(A116, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46086</v>
       </c>
+      <c r="G116">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H116" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J116" t="s">
         <v>1757</v>
       </c>
@@ -21855,6 +22800,14 @@
         <f>_xlfn.XLOOKUP(A117, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46088</v>
       </c>
+      <c r="G117">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H117" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J117" t="s">
         <v>1759</v>
       </c>
@@ -21892,6 +22845,14 @@
         <f>_xlfn.XLOOKUP(A118, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46090</v>
       </c>
+      <c r="G118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H118" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J118" t="s">
         <v>1761</v>
       </c>
@@ -21929,6 +22890,14 @@
         <f>_xlfn.XLOOKUP(A119, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46092</v>
       </c>
+      <c r="G119">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H119" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J119" t="s">
         <v>1763</v>
       </c>
@@ -21966,6 +22935,14 @@
         <f>_xlfn.XLOOKUP(A120, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46094</v>
       </c>
+      <c r="G120">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H120" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J120" t="s">
         <v>1765</v>
       </c>
@@ -22003,6 +22980,14 @@
         <f>_xlfn.XLOOKUP(A121, tblLedger[txn_ref], tblLedger[entry_date], "DATE NOT FOUND")</f>
         <v>46096</v>
       </c>
+      <c r="G121">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H121" t="str">
+        <f t="shared" si="7"/>
+        <v>OK</v>
+      </c>
       <c r="J121" t="s">
         <v>1767</v>
       </c>
@@ -22034,6 +23019,12 @@
       </c>
       <c r="N122" s="18">
         <v>46460.14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G126">
+        <f>COUNTIF(H:H, "OK")</f>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
